--- a/타겟수요.xlsx
+++ b/타겟수요.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\정대원\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\정대원\Desktop\Date_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB4BD580-3A3F-47EB-98D6-4D14506580EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA980B00-8E88-4B38-B925-C19A58D35BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -595,24 +595,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -898,15 +892,15 @@
   <dimension ref="A1:B154"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="29.08203125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="17.4140625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="29.08203125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="17.4140625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -914,7 +908,7 @@
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="1">
         <v>1200</v>
       </c>
     </row>
@@ -922,15 +916,15 @@
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2">
-        <v>621</v>
+      <c r="B3" s="1">
+        <v>443</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>754</v>
       </c>
     </row>
@@ -938,7 +932,7 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>554</v>
       </c>
     </row>
@@ -946,7 +940,7 @@
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>516</v>
       </c>
     </row>
@@ -954,7 +948,7 @@
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="1">
         <v>516</v>
       </c>
     </row>
@@ -962,7 +956,7 @@
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>375</v>
       </c>
     </row>
@@ -970,7 +964,7 @@
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="1">
         <v>1120</v>
       </c>
     </row>
@@ -978,7 +972,7 @@
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="1">
         <v>351</v>
       </c>
     </row>
@@ -986,7 +980,7 @@
       <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="1">
         <v>1198</v>
       </c>
     </row>
@@ -994,7 +988,7 @@
       <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="1">
         <v>665</v>
       </c>
     </row>
@@ -1002,7 +996,7 @@
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="1">
         <v>558</v>
       </c>
     </row>
@@ -1010,7 +1004,7 @@
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="1">
         <v>1963</v>
       </c>
     </row>
@@ -1018,7 +1012,7 @@
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="1">
         <v>666</v>
       </c>
     </row>
@@ -1026,7 +1020,7 @@
       <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="1">
         <v>581</v>
       </c>
     </row>
@@ -1034,7 +1028,7 @@
       <c r="A17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="1">
         <v>332</v>
       </c>
     </row>
@@ -1042,7 +1036,7 @@
       <c r="A18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="1">
         <v>162</v>
       </c>
     </row>
@@ -1050,7 +1044,7 @@
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="1">
         <v>520</v>
       </c>
     </row>
@@ -1058,7 +1052,7 @@
       <c r="A20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="1">
         <v>585</v>
       </c>
     </row>
@@ -1066,7 +1060,7 @@
       <c r="A21" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="1">
         <v>444</v>
       </c>
     </row>
@@ -1074,7 +1068,7 @@
       <c r="A22" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="1">
         <v>350</v>
       </c>
     </row>
@@ -1082,7 +1076,7 @@
       <c r="A23" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="1">
         <v>834</v>
       </c>
     </row>
@@ -1090,7 +1084,7 @@
       <c r="A24" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="1">
         <v>306</v>
       </c>
     </row>
@@ -1098,7 +1092,7 @@
       <c r="A25" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="1">
         <v>262</v>
       </c>
     </row>
@@ -1106,7 +1100,7 @@
       <c r="A26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="1">
         <v>131</v>
       </c>
     </row>
@@ -1114,7 +1108,7 @@
       <c r="A27" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="1">
         <v>374</v>
       </c>
     </row>
@@ -1122,7 +1116,7 @@
       <c r="A28" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="1">
         <v>376</v>
       </c>
     </row>
@@ -1130,7 +1124,7 @@
       <c r="A29" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="1">
         <v>353</v>
       </c>
     </row>
@@ -1138,7 +1132,7 @@
       <c r="A30" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B30" s="1">
         <v>439</v>
       </c>
     </row>
@@ -1146,7 +1140,7 @@
       <c r="A31" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" s="1">
         <v>262</v>
       </c>
     </row>
@@ -1154,7 +1148,7 @@
       <c r="A32" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="1">
         <v>190</v>
       </c>
     </row>
@@ -1162,7 +1156,7 @@
       <c r="A33" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="1">
         <v>226</v>
       </c>
     </row>
@@ -1170,7 +1164,7 @@
       <c r="A34" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="1">
         <v>538</v>
       </c>
     </row>
@@ -1178,7 +1172,7 @@
       <c r="A35" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="1">
         <v>713</v>
       </c>
     </row>
@@ -1186,7 +1180,7 @@
       <c r="A36" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="1">
         <v>944</v>
       </c>
     </row>
@@ -1194,7 +1188,7 @@
       <c r="A37" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="1">
         <v>601</v>
       </c>
     </row>
@@ -1202,7 +1196,7 @@
       <c r="A38" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="1">
         <v>243</v>
       </c>
     </row>
@@ -1210,7 +1204,7 @@
       <c r="A39" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39" s="1">
         <v>867</v>
       </c>
     </row>
@@ -1218,7 +1212,7 @@
       <c r="A40" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B40" s="1">
         <v>235</v>
       </c>
     </row>
@@ -1226,7 +1220,7 @@
       <c r="A41" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" s="1">
         <v>245</v>
       </c>
     </row>
@@ -1234,7 +1228,7 @@
       <c r="A42" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="2">
+      <c r="B42" s="1">
         <v>469</v>
       </c>
     </row>
@@ -1242,7 +1236,7 @@
       <c r="A43" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" s="1">
         <v>612</v>
       </c>
     </row>
@@ -1250,7 +1244,7 @@
       <c r="A44" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44" s="1">
         <v>194</v>
       </c>
     </row>
@@ -1258,7 +1252,7 @@
       <c r="A45" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45" s="1">
         <v>648</v>
       </c>
     </row>
@@ -1266,7 +1260,7 @@
       <c r="A46" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B46" s="2">
+      <c r="B46" s="1">
         <v>598</v>
       </c>
     </row>
@@ -1274,7 +1268,7 @@
       <c r="A47" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="2">
+      <c r="B47" s="1">
         <v>909</v>
       </c>
     </row>
@@ -1282,7 +1276,7 @@
       <c r="A48" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="2">
+      <c r="B48" s="1">
         <v>629</v>
       </c>
     </row>
@@ -1290,7 +1284,7 @@
       <c r="A49" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49" s="1">
         <v>400</v>
       </c>
     </row>
@@ -1298,7 +1292,7 @@
       <c r="A50" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B50" s="1">
         <v>356</v>
       </c>
     </row>
@@ -1306,7 +1300,7 @@
       <c r="A51" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" s="1">
         <v>478</v>
       </c>
     </row>
@@ -1314,7 +1308,7 @@
       <c r="A52" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B52" s="1">
         <v>179</v>
       </c>
     </row>
@@ -1322,7 +1316,7 @@
       <c r="A53" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53" s="1">
         <v>255</v>
       </c>
     </row>
@@ -1330,7 +1324,7 @@
       <c r="A54" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B54" s="1">
         <v>311</v>
       </c>
     </row>
@@ -1338,7 +1332,7 @@
       <c r="A55" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B55" s="2">
+      <c r="B55" s="1">
         <v>253</v>
       </c>
     </row>
@@ -1346,7 +1340,7 @@
       <c r="A56" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56" s="1">
         <v>276</v>
       </c>
     </row>
@@ -1354,7 +1348,7 @@
       <c r="A57" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B57" s="1">
         <v>629</v>
       </c>
     </row>
@@ -1362,7 +1356,7 @@
       <c r="A58" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B58" s="1">
         <v>188</v>
       </c>
     </row>
@@ -1370,7 +1364,7 @@
       <c r="A59" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59" s="1">
         <v>669</v>
       </c>
     </row>
@@ -1378,7 +1372,7 @@
       <c r="A60" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B60" s="1">
         <v>442</v>
       </c>
     </row>
@@ -1386,7 +1380,7 @@
       <c r="A61" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B61" s="2">
+      <c r="B61" s="1">
         <v>532</v>
       </c>
     </row>
@@ -1394,7 +1388,7 @@
       <c r="A62" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B62" s="2">
+      <c r="B62" s="1">
         <v>508</v>
       </c>
     </row>
@@ -1402,7 +1396,7 @@
       <c r="A63" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B63" s="2">
+      <c r="B63" s="1">
         <v>516</v>
       </c>
     </row>
@@ -1410,7 +1404,7 @@
       <c r="A64" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B64" s="2">
+      <c r="B64" s="1">
         <v>367</v>
       </c>
     </row>
@@ -1418,7 +1412,7 @@
       <c r="A65" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B65" s="2">
+      <c r="B65" s="1">
         <v>153</v>
       </c>
     </row>
@@ -1426,7 +1420,7 @@
       <c r="A66" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B66" s="2">
+      <c r="B66" s="1">
         <v>508</v>
       </c>
     </row>
@@ -1434,7 +1428,7 @@
       <c r="A67" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B67" s="2">
+      <c r="B67" s="1">
         <v>225</v>
       </c>
     </row>
@@ -1442,7 +1436,7 @@
       <c r="A68" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B68" s="2">
+      <c r="B68" s="1">
         <v>97</v>
       </c>
     </row>
@@ -1450,7 +1444,7 @@
       <c r="A69" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B69" s="2">
+      <c r="B69" s="1">
         <v>423</v>
       </c>
     </row>
@@ -1458,7 +1452,7 @@
       <c r="A70" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B70" s="2">
+      <c r="B70" s="1">
         <v>363</v>
       </c>
     </row>
@@ -1466,7 +1460,7 @@
       <c r="A71" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B71" s="2">
+      <c r="B71" s="1">
         <v>358</v>
       </c>
     </row>
@@ -1474,7 +1468,7 @@
       <c r="A72" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B72" s="2">
+      <c r="B72" s="1">
         <v>455</v>
       </c>
     </row>
@@ -1482,7 +1476,7 @@
       <c r="A73" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B73" s="2">
+      <c r="B73" s="1">
         <v>246</v>
       </c>
     </row>
@@ -1490,7 +1484,7 @@
       <c r="A74" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B74" s="2">
+      <c r="B74" s="1">
         <v>345</v>
       </c>
     </row>
@@ -1498,7 +1492,7 @@
       <c r="A75" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B75" s="2">
+      <c r="B75" s="1">
         <v>289</v>
       </c>
     </row>
@@ -1506,7 +1500,7 @@
       <c r="A76" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B76" s="2">
+      <c r="B76" s="1">
         <v>418</v>
       </c>
     </row>
@@ -1514,7 +1508,7 @@
       <c r="A77" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B77" s="2">
+      <c r="B77" s="1">
         <v>267</v>
       </c>
     </row>
@@ -1522,7 +1516,7 @@
       <c r="A78" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B78" s="2">
+      <c r="B78" s="1">
         <v>426</v>
       </c>
     </row>
@@ -1530,7 +1524,7 @@
       <c r="A79" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B79" s="2">
+      <c r="B79" s="1">
         <v>834</v>
       </c>
     </row>
@@ -1538,7 +1532,7 @@
       <c r="A80" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B80" s="2">
+      <c r="B80" s="1">
         <v>682</v>
       </c>
     </row>
@@ -1546,7 +1540,7 @@
       <c r="A81" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B81" s="2">
+      <c r="B81" s="1">
         <v>223</v>
       </c>
     </row>
@@ -1554,7 +1548,7 @@
       <c r="A82" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B82" s="2">
+      <c r="B82" s="1">
         <v>1379</v>
       </c>
     </row>
@@ -1562,7 +1556,7 @@
       <c r="A83" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B83" s="2">
+      <c r="B83" s="1">
         <v>165</v>
       </c>
     </row>
@@ -1570,7 +1564,7 @@
       <c r="A84" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B84" s="2">
+      <c r="B84" s="1">
         <v>252</v>
       </c>
     </row>
@@ -1578,7 +1572,7 @@
       <c r="A85" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B85" s="2">
+      <c r="B85" s="1">
         <v>433</v>
       </c>
     </row>
@@ -1586,7 +1580,7 @@
       <c r="A86" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B86" s="2">
+      <c r="B86" s="1">
         <v>220</v>
       </c>
     </row>
@@ -1594,7 +1588,7 @@
       <c r="A87" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B87" s="2">
+      <c r="B87" s="1">
         <v>269</v>
       </c>
     </row>
@@ -1602,7 +1596,7 @@
       <c r="A88" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B88" s="2">
+      <c r="B88" s="1">
         <v>396</v>
       </c>
     </row>
@@ -1610,7 +1604,7 @@
       <c r="A89" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B89" s="2">
+      <c r="B89" s="1">
         <v>215</v>
       </c>
     </row>
@@ -1618,7 +1612,7 @@
       <c r="A90" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B90" s="2">
+      <c r="B90" s="1">
         <v>289</v>
       </c>
     </row>
@@ -1626,7 +1620,7 @@
       <c r="A91" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B91" s="2">
+      <c r="B91" s="1">
         <v>609</v>
       </c>
     </row>
@@ -1634,7 +1628,7 @@
       <c r="A92" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B92" s="2">
+      <c r="B92" s="1">
         <v>380</v>
       </c>
     </row>
@@ -1642,7 +1636,7 @@
       <c r="A93" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B93" s="2">
+      <c r="B93" s="1">
         <v>549</v>
       </c>
     </row>
@@ -1650,7 +1644,7 @@
       <c r="A94" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B94" s="2">
+      <c r="B94" s="1">
         <v>373</v>
       </c>
     </row>
@@ -1658,7 +1652,7 @@
       <c r="A95" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B95" s="2">
+      <c r="B95" s="1">
         <v>668</v>
       </c>
     </row>
@@ -1666,7 +1660,7 @@
       <c r="A96" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B96" s="2">
+      <c r="B96" s="1">
         <v>541</v>
       </c>
     </row>
@@ -1674,7 +1668,7 @@
       <c r="A97" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="2">
+      <c r="B97" s="1">
         <v>293</v>
       </c>
     </row>
@@ -1682,7 +1676,7 @@
       <c r="A98" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B98" s="2">
+      <c r="B98" s="1">
         <v>666</v>
       </c>
     </row>
@@ -1690,7 +1684,7 @@
       <c r="A99" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B99" s="2">
+      <c r="B99" s="1">
         <v>476</v>
       </c>
     </row>
@@ -1698,7 +1692,7 @@
       <c r="A100" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B100" s="2">
+      <c r="B100" s="1">
         <v>396</v>
       </c>
     </row>
@@ -1706,7 +1700,7 @@
       <c r="A101" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B101" s="2">
+      <c r="B101" s="1">
         <v>501</v>
       </c>
     </row>
@@ -1714,7 +1708,7 @@
       <c r="A102" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B102" s="2">
+      <c r="B102" s="1">
         <v>679</v>
       </c>
     </row>
@@ -1722,7 +1716,7 @@
       <c r="A103" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B103" s="2">
+      <c r="B103" s="1">
         <v>556</v>
       </c>
     </row>
@@ -1730,7 +1724,7 @@
       <c r="A104" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B104" s="2">
+      <c r="B104" s="1">
         <v>622</v>
       </c>
     </row>
@@ -1738,7 +1732,7 @@
       <c r="A105" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B105" s="2">
+      <c r="B105" s="1">
         <v>213</v>
       </c>
     </row>
@@ -1746,7 +1740,7 @@
       <c r="A106" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B106" s="2">
+      <c r="B106" s="1">
         <v>253</v>
       </c>
     </row>
@@ -1754,7 +1748,7 @@
       <c r="A107" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B107" s="2">
+      <c r="B107" s="1">
         <v>716</v>
       </c>
     </row>
@@ -1762,7 +1756,7 @@
       <c r="A108" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B108" s="2">
+      <c r="B108" s="1">
         <v>186</v>
       </c>
     </row>
@@ -1770,7 +1764,7 @@
       <c r="A109" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B109" s="2">
+      <c r="B109" s="1">
         <v>488</v>
       </c>
     </row>
@@ -1778,7 +1772,7 @@
       <c r="A110" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B110" s="2">
+      <c r="B110" s="1">
         <v>518</v>
       </c>
     </row>
@@ -1786,7 +1780,7 @@
       <c r="A111" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B111" s="2">
+      <c r="B111" s="1">
         <v>519</v>
       </c>
     </row>
@@ -1794,7 +1788,7 @@
       <c r="A112" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B112" s="2">
+      <c r="B112" s="1">
         <v>317</v>
       </c>
     </row>
@@ -1802,7 +1796,7 @@
       <c r="A113" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B113" s="2">
+      <c r="B113" s="1">
         <v>415</v>
       </c>
     </row>
@@ -1810,7 +1804,7 @@
       <c r="A114" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B114" s="2">
+      <c r="B114" s="1">
         <v>134</v>
       </c>
     </row>
@@ -1818,7 +1812,7 @@
       <c r="A115" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B115" s="2">
+      <c r="B115" s="1">
         <v>317</v>
       </c>
     </row>
@@ -1826,7 +1820,7 @@
       <c r="A116" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B116" s="2">
+      <c r="B116" s="1">
         <v>106</v>
       </c>
     </row>
@@ -1834,7 +1828,7 @@
       <c r="A117" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B117" s="2">
+      <c r="B117" s="1">
         <v>257</v>
       </c>
     </row>
@@ -1842,7 +1836,7 @@
       <c r="A118" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B118" s="2">
+      <c r="B118" s="1">
         <v>213</v>
       </c>
     </row>
@@ -1850,7 +1844,7 @@
       <c r="A119" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B119" s="2">
+      <c r="B119" s="1">
         <v>219</v>
       </c>
     </row>
@@ -1858,7 +1852,7 @@
       <c r="A120" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B120" s="2">
+      <c r="B120" s="1">
         <v>436</v>
       </c>
     </row>
@@ -1866,7 +1860,7 @@
       <c r="A121" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B121" s="2">
+      <c r="B121" s="1">
         <v>118</v>
       </c>
     </row>
@@ -1874,7 +1868,7 @@
       <c r="A122" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B122" s="2">
+      <c r="B122" s="1">
         <v>644</v>
       </c>
     </row>
@@ -1882,7 +1876,7 @@
       <c r="A123" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B123" s="2">
+      <c r="B123" s="1">
         <v>213</v>
       </c>
     </row>
@@ -1890,7 +1884,7 @@
       <c r="A124" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B124" s="2">
+      <c r="B124" s="1">
         <v>210</v>
       </c>
     </row>
@@ -1898,7 +1892,7 @@
       <c r="A125" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B125" s="2">
+      <c r="B125" s="1">
         <v>58</v>
       </c>
     </row>
@@ -1906,7 +1900,7 @@
       <c r="A126" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B126" s="2">
+      <c r="B126" s="1">
         <v>279</v>
       </c>
     </row>
@@ -1914,7 +1908,7 @@
       <c r="A127" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B127" s="2">
+      <c r="B127" s="1">
         <v>386</v>
       </c>
     </row>
@@ -1922,7 +1916,7 @@
       <c r="A128" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B128" s="2">
+      <c r="B128" s="1">
         <v>112</v>
       </c>
     </row>
@@ -1930,7 +1924,7 @@
       <c r="A129" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B129" s="2">
+      <c r="B129" s="1">
         <v>422</v>
       </c>
     </row>
@@ -1938,7 +1932,7 @@
       <c r="A130" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B130" s="2">
+      <c r="B130" s="1">
         <v>373</v>
       </c>
     </row>
@@ -1946,7 +1940,7 @@
       <c r="A131" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B131" s="2">
+      <c r="B131" s="1">
         <v>634</v>
       </c>
     </row>
@@ -1954,7 +1948,7 @@
       <c r="A132" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B132" s="2">
+      <c r="B132" s="1">
         <v>227</v>
       </c>
     </row>
@@ -1962,7 +1956,7 @@
       <c r="A133" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B133" s="2">
+      <c r="B133" s="1">
         <v>407</v>
       </c>
     </row>
@@ -1970,39 +1964,39 @@
       <c r="A134" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B134" s="2">
+      <c r="B134" s="1">
         <v>301</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A135" s="5" t="s">
+      <c r="A135" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B135" s="3">
+      <c r="B135" s="2">
         <v>366</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A136" s="5" t="s">
+      <c r="A136" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B136" s="3">
+      <c r="B136" s="2">
         <v>488</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A137" s="5" t="s">
+      <c r="A137" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B137" s="3">
+      <c r="B137" s="2">
         <v>865</v>
       </c>
     </row>
     <row r="138" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A138" s="5" t="s">
+      <c r="A138" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B138" s="3">
+      <c r="B138" s="2">
         <v>226</v>
       </c>
     </row>
@@ -2010,7 +2004,7 @@
       <c r="A139" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B139" s="2">
+      <c r="B139" s="1">
         <v>322</v>
       </c>
     </row>
@@ -2018,7 +2012,7 @@
       <c r="A140" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B140" s="2">
+      <c r="B140" s="1">
         <v>337</v>
       </c>
     </row>
@@ -2026,7 +2020,7 @@
       <c r="A141" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B141" s="2">
+      <c r="B141" s="1">
         <v>405</v>
       </c>
     </row>
@@ -2034,7 +2028,7 @@
       <c r="A142" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B142" s="2">
+      <c r="B142" s="1">
         <v>371</v>
       </c>
     </row>
@@ -2042,7 +2036,7 @@
       <c r="A143" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B143" s="2">
+      <c r="B143" s="1">
         <v>396</v>
       </c>
     </row>
@@ -2050,7 +2044,7 @@
       <c r="A144" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B144" s="2">
+      <c r="B144" s="1">
         <v>414</v>
       </c>
     </row>
@@ -2058,7 +2052,7 @@
       <c r="A145" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B145" s="2">
+      <c r="B145" s="1">
         <v>277</v>
       </c>
     </row>
@@ -2066,7 +2060,7 @@
       <c r="A146" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B146" s="2">
+      <c r="B146" s="1">
         <v>413</v>
       </c>
     </row>
@@ -2074,7 +2068,7 @@
       <c r="A147" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B147" s="2">
+      <c r="B147" s="1">
         <v>354</v>
       </c>
     </row>
@@ -2082,7 +2076,7 @@
       <c r="A148" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B148" s="2">
+      <c r="B148" s="1">
         <v>283</v>
       </c>
     </row>
@@ -2090,7 +2084,7 @@
       <c r="A149" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B149" s="2">
+      <c r="B149" s="1">
         <v>307</v>
       </c>
     </row>
@@ -2098,7 +2092,7 @@
       <c r="A150" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B150" s="2">
+      <c r="B150" s="1">
         <v>435</v>
       </c>
     </row>
@@ -2106,7 +2100,7 @@
       <c r="A151" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B151" s="2">
+      <c r="B151" s="1">
         <v>456</v>
       </c>
     </row>
@@ -2114,21 +2108,21 @@
       <c r="A152" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B152" s="2">
+      <c r="B152" s="1">
         <v>365</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A153" s="3" t="s">
+      <c r="A153" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B153" s="3">
+      <c r="B153" s="2">
         <v>611</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A154" s="3"/>
-      <c r="B154" s="3"/>
+      <c r="A154" s="2"/>
+      <c r="B154" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
